--- a/data/planilhas/incursao_exemplo.xlsx
+++ b/data/planilhas/incursao_exemplo.xlsx
@@ -287,6 +287,11 @@
     <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <t>Bônus da sala (texto livre). Opcional.</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>Pontos de Organizacao se a sala for superada. 0 ou vazio = nenhum.</t>
       </text>
     </comment>
   </commentList>
@@ -582,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -764,6 +769,30 @@
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Perícias válidas: veja a aba 'Pericias'. Pode escrever com ou sem acento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Pontos de Organização</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Sao do servidor inteiro, nao de cada jogador. Completar o objetivo da 'pontos_conclusao'</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>(aba Incursao) e cada sala superada da o que estiver em 'pontos_organizacao'.</t>
         </is>
       </c>
     </row>
@@ -778,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -900,6 +929,21 @@
       <c r="C7" s="5" t="inlineStr">
         <is>
           <t>MEs por participante ao completar o objetivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>pontos_conclusao</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Pontos que o servidor ganha com a Organizacao ao completar o objetivo.</t>
         </is>
       </c>
     </row>
@@ -914,7 +958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -933,6 +977,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1014,6 +1059,11 @@
       <c r="P1" s="3" t="inlineStr">
         <is>
           <t>recompensa</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>pontos_organizacao</t>
         </is>
       </c>
     </row>
@@ -1074,6 +1124,9 @@
           <t>Quem passa ileso encontra um fragmento do selo.</t>
         </is>
       </c>
+      <c r="Q2" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" ht="62" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
@@ -1132,6 +1185,9 @@
           <t>Revela a CA do chefe antes do confronto final.</t>
         </is>
       </c>
+      <c r="Q3" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -1192,6 +1248,9 @@
         <v>26</v>
       </c>
       <c r="P4" s="6" t="inlineStr"/>
+      <c r="Q4" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -1246,6 +1305,9 @@
       <c r="N5" s="6" t="inlineStr"/>
       <c r="O5" s="6" t="inlineStr"/>
       <c r="P5" s="6" t="inlineStr"/>
+      <c r="Q5" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="62" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
@@ -1296,6 +1358,9 @@
           <t>Cada personagem caído volta com metade do HP máximo.</t>
         </is>
       </c>
+      <c r="Q6" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="62" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -1354,6 +1419,9 @@
           <t>Materiais raros para quem passar no teste.</t>
         </is>
       </c>
+      <c r="Q7" s="6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" ht="62" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
@@ -1414,6 +1482,9 @@
         <v>34</v>
       </c>
       <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" ht="62" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
@@ -1472,6 +1543,9 @@
           <t>O chefe começa o combate final com 10 de HP a menos.</t>
         </is>
       </c>
+      <c r="Q9" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" ht="62" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -1526,6 +1600,9 @@
       <c r="N10" s="6" t="inlineStr"/>
       <c r="O10" s="6" t="inlineStr"/>
       <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
@@ -1591,6 +1668,9 @@
         <is>
           <t>10 MEs por participante + pontos com o Vórtice Oculto</t>
         </is>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/planilhas/incursao_exemplo.xlsx
+++ b/data/planilhas/incursao_exemplo.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Leia-me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Incursao" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Objetivo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Monstros" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -87,6 +88,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -172,6 +174,46 @@
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>Uma linha por campo. Nao apague nem renomeie os campos da coluna A.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Incursoes 2.0</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Criaturas que lutam AO LADO do chefe. O que estiver aqui se soma ao monstro_* da aba Objetivo, ate 6 no total. Deixe vazia para um chefe sozinho.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Quantas iguais. Vazio ou 1 = uma.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Classe de Armadura.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Bonus de ataque (ex.: 5).</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Dado de dano (ex.: 1d8+2).</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Pontos de vida de cada uma.</t>
       </text>
     </comment>
   </commentList>
@@ -618,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -711,74 +753,74 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Tier da incursão, de 1 a 10 (um tier a cada 2 níveis). Só entra quem for deste tier ou de um mais baixo: tier 4 aceita até o nível 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>lore_inicial</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Um selo antigo cedeu sob a cidade e algo do outro lado começou a vazar. Três dias depois, os cães pararam de latir no bairro inteiro e uma rua acordou com as portas trancadas por dentro e ninguém atrás delas.
 O Vórtice Oculto já sabia do selo — foi um dos seus que o fez, há muito tempo. Agora quer o Olho de volta antes que a fenda se alargue o bastante para alguém de fora perceber de quem foi a culpa. Vocês descem hoje.</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Texto de abertura, postado quando a run começa.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>lore_final</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>O Olho para de piscar assim que sai do pedestal, e o silêncio que vem depois é pior que o zumbido. Lá em cima, os cães voltam a latir.
 A Organização recebe o Olho sem cerimônia, como quem recolhe uma ferramenta emprestada. Ninguém menciona o que ele guardava, nem por que o selo tinha a marca de um deles. Vocês recebem o pagamento, e a instrução de não voltar àquela rua.</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Epílogo, postado só quando o grupo cumpre o objetivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>imagem_capa</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>URL da imagem de capa. Opcional.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>recompensa_mes</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>10</v>
-      </c>
+          <t>imagem_capa</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>MEs por participante ao completar o objetivo.</t>
+          <t>URL da imagem de capa. Opcional.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>pontos_conclusao</t>
+          <t>recompensa_mes</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -786,17 +828,36 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
+          <t>MEs por participante ao completar o objetivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>pontos_conclusao</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
           <t>Pontos de Organização que a conclusão rende ao servidor.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Vórtice Oculto,Aliança das Sombras,Guilda dos Mortos,Sentinelas do Alvorecer"</formula1>
     </dataValidation>
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Curta,Média,Longa"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+      <formula1>1</formula1>
+      <formula2>10</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -810,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -936,92 +997,107 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>monstro_ca</t>
+          <t>monstro_quantidade</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Classe de Armadura do chefe.</t>
+          <t>Quantos chefes iguais. Vazio ou 1 = um. O total da sala, contando a aba 'Monstros', nao passa de 6.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>monstro_ataque</t>
+          <t>monstro_ca</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Bônus de ataque do chefe.</t>
+          <t>Classe de Armadura do chefe.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>monstro_dano</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>2d8+4</t>
-        </is>
+          <t>monstro_ataque</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>7</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Dado de dano do chefe (ex.: 2d8+4).</t>
+          <t>Bônus de ataque do chefe.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>monstro_hp</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>58</v>
+          <t>monstro_dano</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2d8+4</t>
+        </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>HP do chefe. Calibre com tools/simular_combate.py.</t>
+          <t>Dado de dano do chefe (ex.: 2d8+4).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>recompensa</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>10 MEs por participante + pontos com o Vórtice Oculto</t>
-        </is>
+          <t>monstro_hp</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>58</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Texto da recompensa.</t>
+          <t>HP do chefe. Calibre com tools/simular_combate.py.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
+          <t>recompensa</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>10 MEs por participante + pontos com o Vórtice Oculto</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Texto da recompensa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
           <t>pontos_organizacao</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Pontos extras da sala final, além de pontos_conclusao.</t>
         </is>
@@ -1030,4 +1106,83 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>quantidade</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>ataque</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>dano</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Acólito do Selo</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1d8+2</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>
--- a/data/planilhas/incursao_exemplo.xlsx
+++ b/data/planilhas/incursao_exemplo.xlsx
@@ -181,6 +181,56 @@
 </file>
 
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Incursoes 2.0</author>
+  </authors>
+  <commentList>
+    <comment ref="A15" authorId="0" shapeId="0">
+      <text>
+        <t>Nome da acao especial do chefe. Vazio = ele so ataca.</t>
+      </text>
+    </comment>
+    <comment ref="A16" authorId="0" shapeId="0">
+      <text>
+        <t>Descricao da acao, mostrada ao grupo. Opcional.</t>
+      </text>
+    </comment>
+    <comment ref="A17" authorId="0" shapeId="0">
+      <text>
+        <t>Atributo que os alvos rolam: FOR, DES, CON, INT, SAB ou CAR.</t>
+      </text>
+    </comment>
+    <comment ref="A18" authorId="0" shapeId="0">
+      <text>
+        <t>CD do teste de resistencia.</t>
+      </text>
+    </comment>
+    <comment ref="A19" authorId="0" shapeId="0">
+      <text>
+        <t>Quantos personagens a acao pega de uma vez. Vazio = 1.</t>
+      </text>
+    </comment>
+    <comment ref="A20" authorId="0" shapeId="0">
+      <text>
+        <t>Rodadas de atordoamento em quem falhar.</t>
+      </text>
+    </comment>
+    <comment ref="A21" authorId="0" shapeId="0">
+      <text>
+        <t>Recharge da 5e: a menor face do d6 que recarrega. 'Recharge 5-6' = 5.</t>
+      </text>
+    </comment>
+    <comment ref="A22" authorId="0" shapeId="0">
+      <text>
+        <t>x = o alvo refaz o save no fim de cada turno e se livra quando passar.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Incursoes 2.0</author>
@@ -871,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -955,7 +1005,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>A câmara é uma esfera perfeita e o Olho flutua no centro dela, aberto. O que o guarda não tem nome porque nada que o viu voltou para dar um.</t>
+          <t>A câmara é uma esfera perfeita e o Olho flutua no centro dela, aberto. O que o guarda não tem nome porque nada que o viu voltou para dar um — e o chão ao redor está cheio de gente de pedra com a mão levantada, como quem tentou explicar alguma coisa.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -985,7 +1035,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Guardião do Selo</t>
+          <t>Medusa</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1016,7 +1066,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -1047,7 +1097,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2d8+4</t>
+          <t>3d8+3+2d6</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1063,7 +1113,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
@@ -1103,8 +1153,97 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>monstro_habilidade</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Petrifying Gaze</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>monstro_habilidade_texto</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>O olhar dela percorre a câmara inteira; ninguém escapa de ser olhado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>monstro_habilidade_save</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>CON</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>monstro_habilidade_cd</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>monstro_habilidade_alvos</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>monstro_habilidade_atordoa</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>monstro_habilidade_recarga</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>monstro_habilidade_save_repete</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1160,25 +1299,25 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Acólito do Selo</t>
+          <t>Nothic</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1d8+2</t>
+          <t>1d10+3</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
